--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 14:39</t>
+          <t>2026-05-08 16:05</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         <v>8.6</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05</t>
+          <t>2026-05-08 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -104,7 +104,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:26</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phantom_Trip_Candidates" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Phantom_Trip_Candidates'!$A$4:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Phantom_Trip_Candidates'!$A$4:$F$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F7FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -105,6 +110,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -498,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:26</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>
@@ -560,8 +574,52 @@
       </c>
       <c r="F5" s="5" t="n"/>
     </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>7432.03</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>No matched trip on this trip_date; OAT rule: charge 1 full trip (review before adding to grand total)</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>7432.03</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>No matched trip on this trip_date; OAT rule: charge 1 full trip (review before adding to grand total)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F5"/>
+  <autoFilter ref="A4:F7"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phantom_Trip_Candidates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Phantom_Trip_Candidates" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Phantom_Trip_Candidates'!$A$4:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Phantom_Trip_Candidates'!$A$4:$F$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -59,11 +59,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F7FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,15 +105,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -486,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -512,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-05-26 13:09</t>
         </is>
       </c>
     </row>
@@ -555,17 +541,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>46142</v>
+        <v>46168</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>8.6</v>
+        <v>2.52</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -574,52 +560,8 @@
       </c>
       <c r="F5" s="5" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>No matched trip on this trip_date; OAT rule: charge 1 full trip (review before adding to grand total)</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>No matched trip on this trip_date; OAT rule: charge 1 full trip (review before adding to grand total)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F7"/>
+  <autoFilter ref="A4:F5"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:09</t>
+          <t>2026-05-26 13:16</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         <v>2.52</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:16</t>
+          <t>2026-05-26 13:20</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         <v>2.52</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>6696.46</v>
+        <v>7543.52</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:20</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>46168</v>
+        <v>46173</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2.52</v>
+        <v>13.11</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7543.52</v>
+        <v>7264</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Phantom_Trip_Candidates" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Phantom_Trip_Candidates'!$A$4:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Phantom_Trip_Candidates'!$A$4:$F$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -88,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,15 +95,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,14 +461,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -498,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>
@@ -538,30 +527,8 @@
       </c>
       <c r="F4" s="4" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>71-8002</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>46173</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>No matched trip on this trip_date; OAT rule: charge 1 full trip (review before adding to grand total)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F5"/>
+  <autoFilter ref="A4:F4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:49</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:49</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 18:21</t>
+          <t>2026-08-04 14:01</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:01</t>
+          <t>2026-08-04 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:33</t>
+          <t>2026-08-04 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:11</t>
+          <t>2026-08-05 14:34</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 14:34</t>
+          <t>2026-08-07 15:55</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 15:55</t>
+          <t>2026-08-09 10:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
+++ b/reports/oatside-pg-2026/exports/13_Phantom_Trip_Candidates.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:57</t>
+          <t>2026-08-09 11:52</t>
         </is>
       </c>
     </row>
